--- a/stories/arbres/ATOM-SAN.ALI.003-01.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.003-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Nora joue dans le jardin. Le soleil chauffe. Nora a soif. Sa bouche est sèche. Papa est près des fleurs. Nora dit : j'ai soif, papa. Papa sourit. Ils vont dans la cuisine. Papa prend un verre. Il verse de l'eau. L'eau est claire. Nora prend le verre d'eau. Elle boit une gorgée. C'est frais. Elle boit encore. Papa dit : quand on a soif, on boit de l'eau. Nora pose le verre. Elle se sent mieux.</t>
+          <t>Nora joue dans le jardin. Le soleil chauffe. Nora a soif. Sa bouche est sèche. Papa est près des fleurs. J'ai soif, papa. Papa sourit. Ils vont dans la cuisine. Papa prend un verre. Il verse de l'eau. L'eau est claire. Nora prend le verre d'eau. Elle boit une gorgée. C'est frais. Elle boit encore. Quand on a soif, on boit de l'eau. Nora pose le verre. Elle se sent mieux.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Nora joue dans le jardin. Le soleil chauffe. Nora a soif. Sa bouche est sèche. Papa est près des fleurs.
+enfant-f|J'ai soif, papa. Papa sourit. Ils vont dans la cuisine. Papa prend un verre. Il verse de l'eau. L'eau est claire.
+narrateur|Nora prend le verre d'eau. Elle boit une gorgée. C'est frais. Elle boit encore.
+papa|Quand on a soif, on boit de l'eau.
+narrateur|Nora pose le verre. Elle se sent mieux.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a soif. Que prend-elle ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Nora avait soif. Elle a pris le verre. Elle a bu de l'eau. Papa était là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1834,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Nora retourne au jardin. Le verre reste sur la table. Merci, dit Nora.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2001,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2041,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.003-01.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.003-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Nora pose le verre. Elle se sent mieux.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Nora a soif. Que prend-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1679,7 @@
           <t>narrateur|Nora avait soif. Elle a pris le verre. Elle a bu de l'eau. Papa était là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1839,6 +1847,7 @@
           <t>narrateur|Nora retourne au jardin. Le verre reste sur la table. Merci, dit Nora.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2006,6 +2015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2048,6 +2058,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2249,6 +2273,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.ALI.003-01.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.003-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le verre d'eau de Nora</t>
+          <t>La dernière goutte de l'arrosoir</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SAN.ALI.002</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>L'arrosoir penche. Une dernière goutte tombe sur la menthe. Nina a soif. Papa verse de l'eau. Elle boit dans un verre.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Nora joue dans le jardin. Le soleil chauffe. Nora a soif. Sa bouche est sèche. Papa est près des fleurs. J'ai soif, papa. Papa sourit. Ils vont dans la cuisine. Papa prend un verre. Il verse de l'eau. L'eau est claire. Nora prend le verre d'eau. Elle boit une gorgée. C'est frais. Elle boit encore. Quand on a soif, on boit de l'eau. Nora pose le verre. Elle se sent mieux.</t>
+          <t>L'arrosoir penche. Une dernière goutte tombe sur la menthe. La menthe sent fort, tout vert. Le soleil chauffe les dalles. Les dalles sont chaudes sous les pieds. Nina habite ici, avec papa. Maman range le linge, tout près. Un oiseau boit dans une soucoupe. Tu as vu l'oiseau, Nina ? Il boit, papa. Oui. Il a soif, lui aussi. On pose l'arrosoir près des fleurs ? Oui, papa. Nina pose l'arrosoir. Le métal est tiède. En ce moment, Nina a soif. Sa bouche est sèche. Sa langue colle un peu. J'ai soif, papa. On va à la cuisine ? Oui. Ils vont dans la cuisine. Le carrelage est frais. Viens. On prend un verre. Papa prend un verre. Le verre est clair. Il verse de l'eau. L'eau chante dans le verre. Tu prends le verre d'eau ? Nina prend le verre. Elle boit une gorgée. C'est frais. Elle boit encore. Quand on a soif, on boit de l'eau. Dans un verre. Nina pose le verre. Tu te sens mieux ? Oui, papa. Bravo, Nina. Tu as bu de l'eau. Une goutte reste sur le bord. Tu as vu la goutte ? Elle brille, papa. Oui. Tout petit soleil. Tu restes près de la table ? Oui. On est bien, ici. Le carrelage est encore frais. Nina tient le verre à deux mains.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1329,64 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Nora joue dans le jardin. Le soleil chauffe. Nora a soif. Sa bouche est sèche. Papa est près des fleurs.
-enfant-f|J'ai soif, papa. Papa sourit. Ils vont dans la cuisine. Papa prend un verre. Il verse de l'eau. L'eau est claire.
-narrateur|Nora prend le verre d'eau. Elle boit une gorgée. C'est frais. Elle boit encore.
+          <t>narrateur|L'arrosoir penche.
+narrateur|Une dernière goutte tombe sur la menthe.
+narrateur|La menthe sent fort, tout vert.
+narrateur|Le soleil chauffe les dalles.
+narrateur|Les dalles sont chaudes sous les pieds.
+narrateur|Nina habite ici, avec papa.
+narrateur|Maman range le linge, tout près.
+narrateur|Un oiseau boit dans une soucoupe.
+papa|Tu as vu l'oiseau, Nina ?
+enfant-f|Il boit, papa.
+papa|Oui.
+papa|Il a soif, lui aussi.
+papa|On pose l'arrosoir près des fleurs ?
+enfant-f|Oui, papa.
+narrateur|Nina pose l'arrosoir.
+narrateur|Le métal est tiède.
+narrateur|En ce moment, Nina a soif.
+narrateur|Sa bouche est sèche.
+narrateur|Sa langue colle un peu.
+enfant-f|J'ai soif, papa.
+papa|On va à la cuisine ?
+enfant-f|Oui.
+narrateur|Ils vont dans la cuisine.
+narrateur|Le carrelage est frais.
+papa|Viens.
+papa|On prend un verre.
+narrateur|Papa prend un verre.
+narrateur|Le verre est clair.
+narrateur|Il verse de l'eau.
+narrateur|L'eau chante dans le verre.
+papa|Tu prends le verre d'eau ?
+narrateur|Nina prend le verre.
+narrateur|Elle boit une gorgée.
+narrateur|C'est frais.
+narrateur|Elle boit encore.
 papa|Quand on a soif, on boit de l'eau.
-narrateur|Nora pose le verre. Elle se sent mieux.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+papa|Dans un verre.
+narrateur|Nina pose le verre.
+papa|Tu te sens mieux ?
+enfant-f|Oui, papa.
+papa|Bravo, Nina.
+papa|Tu as bu de l'eau.
+narrateur|Une goutte reste sur le bord.
+papa|Tu as vu la goutte ?
+enfant-f|Elle brille, papa.
+papa|Oui. Tout petit soleil.
+papa|Tu restes près de la table ?
+enfant-f|Oui.
+papa|On est bien, ici.
+narrateur|Le carrelage est encore frais.
+narrateur|Nina tient le verre à deux mains.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>eau,verre</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,7 +1411,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Nora a soif. Que prend-elle ?</t>
+          <t>Nina a soif. Que prend-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,7 +1571,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Nora a soif. Que prend-elle ?</t>
+          <t>narrateur|Nina a soif.
+narrateur|Que prend-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1532,7 +1600,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nora avait soif. Elle a pris le verre. Elle a bu de l'eau. Papa était là.</t>
+          <t>Nina avait soif. Elle a pris le verre. Elle a bu de l'eau. Bravo. C'est du bon travail. C'est frais, papa. Oui. L'eau est fraîche. Tu veux encore une gorgée ? Oui. Nina boit encore un peu. Elle pose le verre. Le verre reste sur la table ? Oui, papa.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,7 +1744,19 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Nora avait soif. Elle a pris le verre. Elle a bu de l'eau. Papa était là.</t>
+          <t>narrateur|Nina avait soif.
+narrateur|Elle a pris le verre.
+narrateur|Elle a bu de l'eau.
+papa|Bravo.
+papa|C'est du bon travail.
+enfant-f|C'est frais, papa.
+papa|Oui. L'eau est fraîche.
+papa|Tu veux encore une gorgée ?
+enfant-f|Oui.
+narrateur|Nina boit encore un peu.
+narrateur|Elle pose le verre.
+papa|Le verre reste sur la table ?
+enfant-f|Oui, papa.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1704,7 +1784,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nora retourne au jardin. Le verre reste sur la table. Merci, dit Nora.</t>
+          <t>On retourne au jardin ? Oui, papa. Nina prend la main de papa. Le verre reste sur la table. Tu as fini de poser le verre ? Oui. Bravo. Dehors, la menthe sent encore. L'arrosoir reste près des fleurs. L'oiseau a fini de boire, hein ? Oui. Il est parti. Et toi, tu as bu de l'eau. Merci, papa. Merci, Nina. Les dalles sont encore chaudes. On reste un moment près de la menthe ? Oui. Nina reste près de papa. Tes mains sentent la menthe, hein ? Oui. C'est bon. On a bien arrosé. L'arrosoir est vide, maintenant.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1844,7 +1924,29 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Nora retourne au jardin. Le verre reste sur la table. Merci, dit Nora.</t>
+          <t>papa|On retourne au jardin ?
+enfant-f|Oui, papa.
+narrateur|Nina prend la main de papa.
+narrateur|Le verre reste sur la table.
+papa|Tu as fini de poser le verre ?
+enfant-f|Oui.
+papa|Bravo.
+narrateur|Dehors, la menthe sent encore.
+narrateur|L'arrosoir reste près des fleurs.
+papa|L'oiseau a fini de boire, hein ?
+enfant-f|Oui. Il est parti.
+papa|Et toi, tu as bu de l'eau.
+enfant-f|Merci, papa.
+papa|Merci, Nina.
+narrateur|Les dalles sont encore chaudes.
+papa|On reste un moment près de la menthe ?
+enfant-f|Oui.
+narrateur|Nina reste près de papa.
+papa|Tes mains sentent la menthe, hein ?
+enfant-f|Oui.
+enfant-f|C'est bon.
+papa|On a bien arrosé.
+narrateur|L'arrosoir est vide, maintenant.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1872,7 +1974,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'avais soif. J'ai bu de l'eau. Bravo, Nina. Tu as fait du bon travail. La dernière goutte a séché sur la menthe. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2012,7 +2114,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'avais soif.
+enfant-f|J'ai bu de l'eau.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|La dernière goutte a séché sur la menthe.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2034,7 +2141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2179,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.003-01.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.003-01.xlsx
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Nora joue dans le jardin. Le soleil chauffe. Nora a soif. Sa bouche est sèche. Papa est près des fleurs. Nora dit : j'ai soif, papa. Papa sourit. Ils vont dans la cuisine. Papa prend un verre. Il verse de l'&lt;emphasis level="moderate"&gt;eau&lt;/emphasis&gt;. L'eau est claire. Nora prend le verre d'eau. Elle boit une gorgée. C'est frais. Elle boit encore. Papa dit : quand on a soif, on boit de l'eau. Nora pose le verre. Elle se sent mieux.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'arrosoir penche. Une dernière goutte tombe sur la menthe. La menthe sent fort, tout vert. Le soleil chauffe les dalles. Les dalles sont chaudes sous les pieds. Nina habite ici, avec papa. Maman range le linge, tout près. Un oiseau boit dans une soucoupe. Tu as vu l'oiseau, Nina ? Il boit, papa. Oui. Il a soif, lui aussi. On pose l'arrosoir près des fleurs ? Oui, papa. Nina pose l'arrosoir. Le métal est tiède. En ce moment, Nina a soif. Sa bouche est sèche. Sa langue colle un peu. J'ai soif, papa. On va à la cuisine ? Oui. Ils vont dans la cuisine. Le carrelage est frais. Viens. On prend un verre. Papa prend un verre. Le verre est clair. Il verse de l'eau. L'eau chante dans le verre. Tu prends le verre d'eau ? Nina prend le verre. Elle boit une gorgée. C'est frais. Elle boit encore. Quand on a soif, on boit de l'eau. Dans un verre. Nina pose le verre. Tu te sens mieux ? Oui, papa. Bravo, Nina. Tu as bu de l'eau. Une goutte reste sur le bord. Tu as vu la goutte ? Elle brille, papa. Oui. Tout petit soleil. Tu restes près de la table ? Oui. On est bien, ici. Le carrelage est encore frais. Nina tient le verre à deux mains.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Nora a &lt;emphasis level="moderate"&gt;soif&lt;/emphasis&gt;. Que prend-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina a soif. Que prend-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1575,7 +1575,6 @@
 narrateur|Que prend-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1600,12 +1599,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nina avait soif. Elle a pris le verre. Elle a bu de l'eau. Bravo. C'est du bon travail. C'est frais, papa. Oui. L'eau est fraîche. Tu veux encore une gorgée ? Oui. Nina boit encore un peu. Elle pose le verre. Le verre reste sur la table ? Oui, papa.</t>
+          <t>Nina avait soif. Elle a pris le verre. Elle a bu de l'eau. Bravo. C'est frais, papa. Oui. L'eau est fraîche. Tu veux encore une gorgée ? Oui. Nina boit encore un peu. Elle pose le verre. Le verre reste sur la table ? Oui, papa.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Nora avait soif. Elle a pris le verre. Elle a bu de l'&lt;emphasis level="moderate"&gt;eau&lt;/emphasis&gt;. Papa était là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina avait soif. Elle a pris le verre. Elle a bu de l'eau. Bravo. C'est frais, papa. Oui. L'eau est fraîche. Tu veux encore une gorgée ? Oui. Nina boit encore un peu. Elle pose le verre. Le verre reste sur la table ? Oui, papa.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1748,7 +1747,6 @@
 narrateur|Elle a pris le verre.
 narrateur|Elle a bu de l'eau.
 papa|Bravo.
-papa|C'est du bon travail.
 enfant-f|C'est frais, papa.
 papa|Oui. L'eau est fraîche.
 papa|Tu veux encore une gorgée ?
@@ -1759,7 +1757,6 @@
 enfant-f|Oui, papa.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1789,7 +1786,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Nora retourne au jardin. Le &lt;emphasis level="moderate"&gt;verre&lt;/emphasis&gt; reste sur la table. Merci, dit Nora.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>On retourne au jardin ? Oui, papa. Nina prend la main de papa. Le verre reste sur la table. Tu as fini de poser le verre ? Oui. Bravo. Dehors, la menthe sent encore. L'arrosoir reste près des fleurs. L'oiseau a fini de boire, hein ? Oui. Il est parti. Et toi, tu as bu de l'eau. Merci, papa. Merci, Nina. Les dalles sont encore chaudes. On reste un moment près de la menthe ? Oui. Nina reste près de papa. Tes mains sentent la menthe, hein ? Oui. C'est bon. On a bien arrosé. L'arrosoir est vide, maintenant.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1949,7 +1946,6 @@
 narrateur|L'arrosoir est vide, maintenant.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1974,12 +1970,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'avais soif. J'ai bu de l'eau. Bravo, Nina. Tu as fait du bon travail. La dernière goutte a séché sur la menthe. L'histoire est finie.</t>
+          <t>J'avais soif. J'ai bu de l'eau. Bravo, Nina. La dernière goutte a séché sur la menthe.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'avais soif. J'ai bu de l'eau. Bravo, Nina. La dernière goutte a séché sur la menthe.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2117,12 +2113,9 @@
           <t>enfant-f|J'avais soif.
 enfant-f|J'ai bu de l'eau.
 papa|Bravo, Nina.
-papa|Tu as fait du bon travail.
-narrateur|La dernière goutte a séché sur la menthe.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La dernière goutte a séché sur la menthe.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2141,7 +2134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2186,6 +2179,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.003-01.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.003-01.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin</t>
+          <t>jardin puis cuisine</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nora, papa</t>
+          <t>Nina, papa</t>
         </is>
       </c>
     </row>
